--- a/evaluation_forms/010_preventive_screening_program_evaluation_form--evaluation_forms.xlsx
+++ b/evaluation_forms/010_preventive_screening_program_evaluation_form--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'clinic'}</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Clinic'}</t>
+          <t>Clinic</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'hospital'}</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Hospital'}</t>
+          <t>Hospital</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'wellness_program'}</t>
+          <t>wellness_program</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Wellness Program'}</t>
+          <t>Wellness Program</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'blood_pressure'}</t>
+          <t>blood_pressure</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Blood Pressure'}</t>
+          <t>Blood Pressure</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cholesterol'}</t>
+          <t>cholesterol</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Cholesterol'}</t>
+          <t>Cholesterol</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'diabetes'}</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Diabetes'}</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
